--- a/assets/files/infosys-financial-model.xlsx
+++ b/assets/files/infosys-financial-model.xlsx
@@ -15,7 +15,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ratios" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peer Comps" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Cover'!$A$1:$F$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A$1:$J$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Historical'!$A$1:$J$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Forecast'!$A$1:$H$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'DCF'!$A$1:$H$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Ratios'!$A$1:$J$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Peer Comps'!$A$1:$G$37</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
 </file>
@@ -456,7 +464,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="235">
+  <cellXfs count="238">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1106,6 +1114,9 @@
     <xf numFmtId="3" fontId="29" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="29" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="24" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1358,7 +1369,7 @@
   <sheetPr filterMode="0">
     <tabColor rgb="FF007CC3"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
@@ -1427,7 +1438,6 @@
       <c r="E6" s="167" t="n"/>
       <c r="F6" s="167" t="n"/>
     </row>
-    <row r="7"/>
     <row r="8" ht="15" customHeight="1" s="67">
       <c r="B8" s="168" t="inlineStr">
         <is>
@@ -1435,7 +1445,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10" ht="15" customHeight="1" s="67">
       <c r="A10" s="169" t="inlineStr">
         <is>
@@ -1525,8 +1534,6 @@
         <v/>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19"/>
     <row r="20" ht="15" customHeight="1" s="67">
       <c r="A20" s="169" t="inlineStr">
         <is>
@@ -1581,8 +1588,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28"/>
     <row r="29" ht="15" customHeight="1" s="67">
       <c r="B29" s="168" t="inlineStr">
         <is>
@@ -1592,8 +1597,8 @@
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -1602,7 +1607,7 @@
   <sheetPr filterMode="0">
     <tabColor rgb="FF007CC3"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
@@ -1678,11 +1683,11 @@
     <row r="5" ht="15" customHeight="1" s="67">
       <c r="A5" s="184" t="inlineStr">
         <is>
-          <t>Current share price (₹, 03-Jul-2026)</t>
+          <t>Current share price (₹, 18-Jul-2026)</t>
         </is>
       </c>
       <c r="B5" s="185" t="n">
-        <v>1040.9</v>
+        <v>1096.5</v>
       </c>
       <c r="C5" s="89" t="n"/>
       <c r="D5" s="89" t="n"/>
@@ -2040,8 +2045,8 @@
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -2050,7 +2055,7 @@
   <sheetPr filterMode="0">
     <tabColor rgb="FF007CC3"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
@@ -3372,8 +3377,8 @@
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -3382,7 +3387,7 @@
   <sheetPr filterMode="0">
     <tabColor rgb="FF007CC3"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
@@ -3825,8 +3830,8 @@
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -3835,7 +3840,7 @@
   <sheetPr filterMode="0">
     <tabColor rgb="FF007CC3"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
@@ -4404,8 +4409,8 @@
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -4414,7 +4419,7 @@
   <sheetPr filterMode="0">
     <tabColor rgb="FF007CC3"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
@@ -4921,8 +4926,8 @@
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -4931,9 +4936,9 @@
   <sheetPr filterMode="0">
     <tabColor rgb="FF007CC3"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="42" customWidth="1" style="66" min="1" max="1"/>
@@ -5024,7 +5029,7 @@
         </is>
       </c>
       <c r="B5" s="185" t="n">
-        <v>1040.9</v>
+        <v>1096.5</v>
       </c>
       <c r="C5" s="185" t="n">
         <v>72.59</v>
@@ -5051,7 +5056,7 @@
         </is>
       </c>
       <c r="B6" s="185" t="n">
-        <v>2150</v>
+        <v>2190</v>
       </c>
       <c r="C6" s="185" t="n">
         <v>136.01</v>
@@ -5168,7 +5173,6 @@
       <c r="F11" s="183" t="n"/>
       <c r="G11" s="183" t="n"/>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="224" t="inlineStr">
         <is>
@@ -5215,11 +5219,10 @@
         <v/>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="224" t="inlineStr">
         <is>
-          <t>VALUATION TRIANGULATION — FOOTBALL FIELD</t>
+          <t>VALUATION TRIANGULATION — FOOTBALL FIELD (multi-method)</t>
         </is>
       </c>
       <c r="B18" s="161" t="n"/>
@@ -5254,7 +5257,7 @@
     <row r="20">
       <c r="A20" s="212" t="inlineStr">
         <is>
-          <t>DCF (intrinsic)</t>
+          <t>DCF (FCFF, intrinsic)</t>
         </is>
       </c>
       <c r="B20" s="230">
@@ -5273,7 +5276,7 @@
     <row r="21">
       <c r="A21" s="231" t="inlineStr">
         <is>
-          <t>Comparable companies</t>
+          <t>Comparable companies — P/E</t>
         </is>
       </c>
       <c r="B21" s="228">
@@ -5292,42 +5295,149 @@
     <row r="22">
       <c r="A22" s="225" t="inlineStr">
         <is>
-          <t>Blended target (70% intrinsic / 30% comps)</t>
-        </is>
+          <t>EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="B22" s="235">
+        <f>B33*0.9</f>
+        <v/>
       </c>
       <c r="C22" s="232">
-        <f>0.7*DCF!B18+0.3*B16</f>
+        <f>B33</f>
+        <v/>
+      </c>
+      <c r="D22" s="235">
+        <f>B33*1.1</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="231" t="inlineStr">
         <is>
-          <t>Current market price (₹)</t>
+          <t>Blended target (70% DCF / 30% relative)</t>
         </is>
       </c>
       <c r="C23" s="228">
-        <f>B5</f>
+        <f>0.7*DCF!B18+0.3*AVERAGE(B16,B33)</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="225" t="inlineStr">
         <is>
+          <t>Current market price (₹)</t>
+        </is>
+      </c>
+      <c r="C24" s="233">
+        <f>B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="66" t="inlineStr">
+        <is>
           <t>Implied upside / (downside)</t>
         </is>
       </c>
-      <c r="C24" s="233">
-        <f>C22/B5-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25"/>
+      <c r="C25" s="236">
+        <f>C23/B5-1</f>
+        <v/>
+      </c>
+    </row>
     <row r="26">
       <c r="A26" s="234" t="inlineStr">
         <is>
-          <t>Peer multiples researched as of Jun 2026 (Kotak price to be verified). Refresh peer inputs before publication.</t>
-        </is>
+          <t>Peer prices as of Jun 2026 (IT sector fell further in Jul; refresh before publication). Infosys live 18-Jul-2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="224" t="inlineStr">
+        <is>
+          <t>MARKET MULTIPLE — EV/EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="225" t="inlineStr">
+        <is>
+          <t>FY26 EBITDA (₹ Cr)</t>
+        </is>
+      </c>
+      <c r="B29" s="228" t="n">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="225" t="inlineStr">
+        <is>
+          <t>Justified EV/EBITDA (x) — de-rated sector</t>
+        </is>
+      </c>
+      <c r="B30" s="226" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="225" t="inlineStr">
+        <is>
+          <t>Enterprise value = mult × EBITDA (₹ Cr)</t>
+        </is>
+      </c>
+      <c r="B31" s="228">
+        <f>B30*B29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="225" t="inlineStr">
+        <is>
+          <t>Add: net cash (₹ Cr)</t>
+        </is>
+      </c>
+      <c r="B32" s="228">
+        <f>-Assumptions!B8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="225" t="inlineStr">
+        <is>
+          <t>EV/EBITDA-implied value / share (₹)</t>
+        </is>
+      </c>
+      <c r="B33" s="228">
+        <f>(B31+B32)/Assumptions!B6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="224" t="inlineStr">
+        <is>
+          <t>CROSS-CHECK — FCF YIELD</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="225" t="inlineStr">
+        <is>
+          <t>FY27E FCFF (₹ Cr)</t>
+        </is>
+      </c>
+      <c r="B36" s="228">
+        <f>Forecast!C16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="225" t="inlineStr">
+        <is>
+          <t>FCF yield = FCFF / market cap</t>
+        </is>
+      </c>
+      <c r="B37" s="237">
+        <f>B36/Assumptions!B7</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -5336,7 +5446,7 @@
     <mergeCell ref="A18:G18"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>